--- a/public/templates/leads-import-template.xlsx
+++ b/public/templates/leads-import-template.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>SEIKI — Modèle d'import de leads</t>
+  </si>
   <si>
     <t>Nom de la société</t>
   </si>
@@ -77,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -87,14 +90,24 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFD4C4A8"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF141414"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -109,9 +122,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,79 +467,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I3" t="s">
         <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" errorTitle="Segment invalide" error="Merci de choisir Media, Retail ou Instit." sqref="B2:B1000">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Segment invalide" error="Merci de choisir Media, Retail ou Instit." sqref="B3:B1000">
       <formula1>"Media,Retail,Instit"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/leads-import-template.xlsx
+++ b/public/templates/leads-import-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>SEIKI — Modèle d'import de leads</t>
   </si>
@@ -19,12 +19,18 @@
     <t>Nom de la société</t>
   </si>
   <si>
+    <t>Genre</t>
+  </si>
+  <si>
+    <t>Prénom</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
     <t>Segment</t>
   </si>
   <si>
-    <t>Nom du contact</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
@@ -49,10 +55,16 @@
     <t>Acme Corp</t>
   </si>
   <si>
+    <t>M.</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>DUPONT</t>
+  </si>
+  <si>
     <t>Retail</t>
-  </si>
-  <si>
-    <t>Jean Dupont</t>
   </si>
   <si>
     <t>jean.dupont@acme.com</t>
@@ -467,13 +479,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="10" width="24" customWidth="1"/>
+    <col min="1" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,8 +498,10 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -518,45 +532,57 @@
       <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" errorTitle="Segment invalide" error="Merci de choisir Media, Retail ou Instit." sqref="B3:B1000">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Segment invalide" error="Merci de choisir Media, Retail ou Instit." sqref="E3:E1000">
       <formula1>"Media,Retail,Instit"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/leads-import-template.xlsx
+++ b/public/templates/leads-import-template.xlsx
@@ -581,7 +581,10 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Genre invalide" error="Merci de choisir M., Mme ou Autre (ou laisser vide)." sqref="B3:B1000">
+      <formula1>"M.,Mme,Autre"</formula1>
+    </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Segment invalide" error="Merci de choisir Media, Retail ou Instit." sqref="E3:E1000">
       <formula1>"Media,Retail,Instit"</formula1>
     </dataValidation>

--- a/public/templates/leads-import-template.xlsx
+++ b/public/templates/leads-import-template.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82437145-BF96-40EF-827C-C85418A51384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Leads" state="visible" r:id="rId4"/>
+    <sheet name="Leads" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>SEIKI — Modèle d'import de leads</t>
   </si>
@@ -52,64 +56,54 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Acme Corp</t>
-  </si>
-  <si>
     <t>M.</t>
   </si>
   <si>
-    <t>Jean</t>
-  </si>
-  <si>
-    <t>DUPONT</t>
-  </si>
-  <si>
     <t>Retail</t>
-  </si>
-  <si>
-    <t>jean.dupont@acme.com</t>
-  </si>
-  <si>
-    <t>+33612345678</t>
-  </si>
-  <si>
-    <t>https://linkedin.com/in/jeandupont</t>
-  </si>
-  <si>
-    <t>https://acme.com</t>
-  </si>
-  <si>
-    <t>LinkedIn</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Rencontré au salon X</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
       <color rgb="FFD4C4A8"/>
-      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -121,8 +115,14 @@
         <fgColor rgb="FF141414"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6B5FE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -130,16 +130,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,103 +499,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="23.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -582,14 +573,14 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Genre invalide" error="Merci de choisir M., Mme ou Autre (ou laisser vide)." sqref="B3:B1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Genre invalide" error="Merci de choisir M., Mme ou Autre (ou laisser vide)." sqref="B3:B1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"M.,Mme,Autre"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="Segment invalide" error="Merci de choisir Media, Retail ou Instit." sqref="E3:E1000">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Segment invalide" error="Merci de choisir Media, Retail ou Instit." sqref="E3:E1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Media,Retail,Instit"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>